--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/INTERRUPTOR FREIO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/INTERRUPTOR FREIO - 01_02.xlsx
@@ -457,7 +457,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +482,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -524,7 +532,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +557,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +582,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +632,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +657,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,7 +682,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -671,7 +707,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -692,7 +732,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -763,7 +807,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -784,7 +832,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -805,7 +857,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20.82</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -826,7 +882,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -847,7 +907,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -868,7 +932,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/INTERRUPTOR FREIO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/INTERRUPTOR FREIO - 01_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -832,11 +752,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -857,11 +772,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>20.82</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -882,11 +792,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -907,11 +812,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -930,11 +830,6 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
     </row>
